--- a/frontend/assets/baustellen-import-vorlage.xlsx
+++ b/frontend/assets/baustellen-import-vorlage.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Baustellen" sheetId="1" r:id="R50c2e130bec54358"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hinweise" sheetId="2" r:id="R92f19d46836a4c65"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Baustellen" sheetId="1" r:id="R5b38356b869c4140"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hinweise" sheetId="2" r:id="R721251246ade4d84"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -17,20 +17,20 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="@"/>
   </x:numFmts>
-  <x:fonts count="4">
+  <x:fonts count="7">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="16"/>
+      <x:sz val="18"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
       <x:sz val="11"/>
-      <x:color rgb="FF7D0B12"/>
+      <x:color rgb="FF9C101C"/>
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
@@ -39,8 +39,24 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF151515"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF151515"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="12"/>
+      <x:color rgb="FF9C101C"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -54,35 +70,92 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFDEBED"/>
+        <x:fgColor rgb="FFFDE9EC"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFE30613"/>
+        <x:fgColor rgb="FFED0011"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="3">
+  <x:borders count="11">
     <x:border/>
     <x:border>
       <x:bottom style="thin">
-        <x:color rgb="FFE2E2E2"/>
+        <x:color rgb="FFE3E3E3"/>
       </x:bottom>
     </x:border>
     <x:border>
       <x:top style="thin">
-        <x:color rgb="FFE2E2E2"/>
+        <x:color rgb="FFE3E3E3"/>
       </x:top>
       <x:bottom style="thin">
-        <x:color rgb="FFE2E2E2"/>
+        <x:color rgb="FFE3E3E3"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFF5BCC2"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFF5BCC2"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FFF5BCC2"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFF5BCC2"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFF5BCC2"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFF5BCC2"/>
+      </x:left>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFF5BCC2"/>
+      </x:right>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFF5BCC2"/>
+      </x:left>
+      <x:bottom style="thin">
+        <x:color rgb="FFF5BCC2"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:bottom style="thin">
+        <x:color rgb="FFF5BCC2"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFF5BCC2"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFF5BCC2"/>
       </x:bottom>
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="16">
+  <x:cellXfs count="57">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -97,23 +170,142 @@
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="4" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BaustellenImport" displayName="BaustellenImport" ref="A5:G205" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A5:G205"/>
+  <x:tableColumns count="7">
+    <x:tableColumn id="1" name="Kunde"/>
+    <x:tableColumn id="2" name="Baustelle"/>
+    <x:tableColumn id="3" name="Aufgabe"/>
+    <x:tableColumn id="4" name="Straße"/>
+    <x:tableColumn id="5" name="Hausnummer"/>
+    <x:tableColumn id="6" name="PLZ"/>
+    <x:tableColumn id="7" name="Ort"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -311,14 +503,13 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="28" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="27" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="29" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="26" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="15" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="23" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
@@ -331,9 +522,8 @@
       <x:c r="E1" s="3"/>
       <x:c r="F1" s="3"/>
       <x:c r="G1" s="3"/>
-      <x:c r="H1" s="3"/>
-    </x:row>
-    <x:row r="3" ht="27" customHeight="1">
+    </x:row>
+    <x:row r="3" ht="28" customHeight="1">
       <x:c r="A3" s="6" t="str">
         <x:v>Ab Zeile 6 eintragen. Pflicht: Kunde, Baustelle, Straße, Hausnummer, PLZ und Ort.</x:v>
       </x:c>
@@ -343,240 +533,1839 @@
       <x:c r="E3" s="6"/>
       <x:c r="F3" s="6"/>
       <x:c r="G3" s="6"/>
-      <x:c r="H3" s="6"/>
-    </x:row>
-    <x:row r="5" ht="28" customHeight="1">
-      <x:c r="A5" s="10" t="str">
+    </x:row>
+    <x:row r="5" ht="26" customHeight="1">
+      <x:c r="A5" s="9" t="str">
         <x:v>Kunde</x:v>
       </x:c>
-      <x:c r="B5" s="10" t="str">
+      <x:c r="B5" s="9" t="str">
         <x:v>Baustelle</x:v>
       </x:c>
-      <x:c r="C5" s="10" t="str">
-        <x:v>Projekt</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="str">
+      <x:c r="C5" s="9" t="str">
         <x:v>Aufgabe</x:v>
       </x:c>
-      <x:c r="E5" s="10" t="str">
+      <x:c r="D5" s="9" t="str">
         <x:v>Straße</x:v>
       </x:c>
-      <x:c r="F5" s="10" t="str">
+      <x:c r="E5" s="9" t="str">
         <x:v>Hausnummer</x:v>
       </x:c>
-      <x:c r="G5" s="10" t="str">
+      <x:c r="F5" s="9" t="str">
         <x:v>PLZ</x:v>
       </x:c>
-      <x:c r="H5" s="10" t="str">
+      <x:c r="G5" s="9" t="str">
         <x:v>Ort</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="11"/>
-      <x:c r="B6" s="11"/>
-      <x:c r="C6" s="11"/>
-      <x:c r="D6" s="11"/>
-      <x:c r="E6" s="11"/>
-      <x:c r="F6" s="11"/>
-      <x:c r="G6" s="13"/>
-      <x:c r="H6" s="11"/>
+      <x:c r="A6" s="14"/>
+      <x:c r="B6" s="14"/>
+      <x:c r="C6" s="14"/>
+      <x:c r="D6" s="14"/>
+      <x:c r="E6" s="14"/>
+      <x:c r="F6" s="16"/>
+      <x:c r="G6" s="14"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="12"/>
-      <x:c r="B7" s="12"/>
-      <x:c r="C7" s="12"/>
-      <x:c r="D7" s="12"/>
-      <x:c r="E7" s="12"/>
-      <x:c r="F7" s="12"/>
-      <x:c r="G7" s="14"/>
-      <x:c r="H7" s="12"/>
+      <x:c r="A7" s="15"/>
+      <x:c r="B7" s="15"/>
+      <x:c r="C7" s="15"/>
+      <x:c r="D7" s="15"/>
+      <x:c r="E7" s="15"/>
+      <x:c r="F7" s="17"/>
+      <x:c r="G7" s="15"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="12"/>
-      <x:c r="B8" s="12"/>
-      <x:c r="C8" s="12"/>
-      <x:c r="D8" s="12"/>
-      <x:c r="E8" s="12"/>
-      <x:c r="F8" s="12"/>
-      <x:c r="G8" s="14"/>
-      <x:c r="H8" s="12"/>
+      <x:c r="A8" s="15"/>
+      <x:c r="B8" s="15"/>
+      <x:c r="C8" s="15"/>
+      <x:c r="D8" s="15"/>
+      <x:c r="E8" s="15"/>
+      <x:c r="F8" s="17"/>
+      <x:c r="G8" s="15"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="12"/>
-      <x:c r="B9" s="12"/>
-      <x:c r="C9" s="12"/>
-      <x:c r="D9" s="12"/>
-      <x:c r="E9" s="12"/>
-      <x:c r="F9" s="12"/>
-      <x:c r="G9" s="14"/>
-      <x:c r="H9" s="12"/>
+      <x:c r="A9" s="15"/>
+      <x:c r="B9" s="15"/>
+      <x:c r="C9" s="15"/>
+      <x:c r="D9" s="15"/>
+      <x:c r="E9" s="15"/>
+      <x:c r="F9" s="17"/>
+      <x:c r="G9" s="15"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="12"/>
-      <x:c r="B10" s="12"/>
-      <x:c r="C10" s="12"/>
-      <x:c r="D10" s="12"/>
-      <x:c r="E10" s="12"/>
-      <x:c r="F10" s="12"/>
-      <x:c r="G10" s="14"/>
-      <x:c r="H10" s="12"/>
+      <x:c r="A10" s="15"/>
+      <x:c r="B10" s="15"/>
+      <x:c r="C10" s="15"/>
+      <x:c r="D10" s="15"/>
+      <x:c r="E10" s="15"/>
+      <x:c r="F10" s="17"/>
+      <x:c r="G10" s="15"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="12"/>
-      <x:c r="B11" s="12"/>
-      <x:c r="C11" s="12"/>
-      <x:c r="D11" s="12"/>
-      <x:c r="E11" s="12"/>
-      <x:c r="F11" s="12"/>
-      <x:c r="G11" s="14"/>
-      <x:c r="H11" s="12"/>
+      <x:c r="A11" s="15"/>
+      <x:c r="B11" s="15"/>
+      <x:c r="C11" s="15"/>
+      <x:c r="D11" s="15"/>
+      <x:c r="E11" s="15"/>
+      <x:c r="F11" s="17"/>
+      <x:c r="G11" s="15"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="12"/>
-      <x:c r="B12" s="12"/>
-      <x:c r="C12" s="12"/>
-      <x:c r="D12" s="12"/>
-      <x:c r="E12" s="12"/>
-      <x:c r="F12" s="12"/>
-      <x:c r="G12" s="14"/>
-      <x:c r="H12" s="12"/>
+      <x:c r="A12" s="15"/>
+      <x:c r="B12" s="15"/>
+      <x:c r="C12" s="15"/>
+      <x:c r="D12" s="15"/>
+      <x:c r="E12" s="15"/>
+      <x:c r="F12" s="17"/>
+      <x:c r="G12" s="15"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="12"/>
-      <x:c r="B13" s="12"/>
-      <x:c r="C13" s="12"/>
-      <x:c r="D13" s="12"/>
-      <x:c r="E13" s="12"/>
-      <x:c r="F13" s="12"/>
-      <x:c r="G13" s="14"/>
-      <x:c r="H13" s="12"/>
+      <x:c r="A13" s="15"/>
+      <x:c r="B13" s="15"/>
+      <x:c r="C13" s="15"/>
+      <x:c r="D13" s="15"/>
+      <x:c r="E13" s="15"/>
+      <x:c r="F13" s="17"/>
+      <x:c r="G13" s="15"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="12"/>
-      <x:c r="B14" s="12"/>
-      <x:c r="C14" s="12"/>
-      <x:c r="D14" s="12"/>
-      <x:c r="E14" s="12"/>
-      <x:c r="F14" s="12"/>
-      <x:c r="G14" s="14"/>
-      <x:c r="H14" s="12"/>
+      <x:c r="A14" s="15"/>
+      <x:c r="B14" s="15"/>
+      <x:c r="C14" s="15"/>
+      <x:c r="D14" s="15"/>
+      <x:c r="E14" s="15"/>
+      <x:c r="F14" s="17"/>
+      <x:c r="G14" s="15"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="12"/>
-      <x:c r="B15" s="12"/>
-      <x:c r="C15" s="12"/>
-      <x:c r="D15" s="12"/>
-      <x:c r="E15" s="12"/>
-      <x:c r="F15" s="12"/>
-      <x:c r="G15" s="14"/>
-      <x:c r="H15" s="12"/>
+      <x:c r="A15" s="15"/>
+      <x:c r="B15" s="15"/>
+      <x:c r="C15" s="15"/>
+      <x:c r="D15" s="15"/>
+      <x:c r="E15" s="15"/>
+      <x:c r="F15" s="17"/>
+      <x:c r="G15" s="15"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="12"/>
-      <x:c r="B16" s="12"/>
-      <x:c r="C16" s="12"/>
-      <x:c r="D16" s="12"/>
-      <x:c r="E16" s="12"/>
-      <x:c r="F16" s="12"/>
-      <x:c r="G16" s="14"/>
-      <x:c r="H16" s="12"/>
+      <x:c r="A16" s="15"/>
+      <x:c r="B16" s="15"/>
+      <x:c r="C16" s="15"/>
+      <x:c r="D16" s="15"/>
+      <x:c r="E16" s="15"/>
+      <x:c r="F16" s="17"/>
+      <x:c r="G16" s="15"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="12"/>
-      <x:c r="B17" s="12"/>
-      <x:c r="C17" s="12"/>
-      <x:c r="D17" s="12"/>
-      <x:c r="E17" s="12"/>
-      <x:c r="F17" s="12"/>
-      <x:c r="G17" s="14"/>
-      <x:c r="H17" s="12"/>
+      <x:c r="A17" s="15"/>
+      <x:c r="B17" s="15"/>
+      <x:c r="C17" s="15"/>
+      <x:c r="D17" s="15"/>
+      <x:c r="E17" s="15"/>
+      <x:c r="F17" s="17"/>
+      <x:c r="G17" s="15"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="12"/>
-      <x:c r="B18" s="12"/>
-      <x:c r="C18" s="12"/>
-      <x:c r="D18" s="12"/>
-      <x:c r="E18" s="12"/>
-      <x:c r="F18" s="12"/>
-      <x:c r="G18" s="14"/>
-      <x:c r="H18" s="12"/>
+      <x:c r="A18" s="15"/>
+      <x:c r="B18" s="15"/>
+      <x:c r="C18" s="15"/>
+      <x:c r="D18" s="15"/>
+      <x:c r="E18" s="15"/>
+      <x:c r="F18" s="17"/>
+      <x:c r="G18" s="15"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="12"/>
-      <x:c r="B19" s="12"/>
-      <x:c r="C19" s="12"/>
-      <x:c r="D19" s="12"/>
-      <x:c r="E19" s="12"/>
-      <x:c r="F19" s="12"/>
-      <x:c r="G19" s="14"/>
-      <x:c r="H19" s="12"/>
+      <x:c r="A19" s="15"/>
+      <x:c r="B19" s="15"/>
+      <x:c r="C19" s="15"/>
+      <x:c r="D19" s="15"/>
+      <x:c r="E19" s="15"/>
+      <x:c r="F19" s="17"/>
+      <x:c r="G19" s="15"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="12"/>
-      <x:c r="B20" s="12"/>
-      <x:c r="C20" s="12"/>
-      <x:c r="D20" s="12"/>
-      <x:c r="E20" s="12"/>
-      <x:c r="F20" s="12"/>
-      <x:c r="G20" s="14"/>
-      <x:c r="H20" s="12"/>
+      <x:c r="A20" s="15"/>
+      <x:c r="B20" s="15"/>
+      <x:c r="C20" s="15"/>
+      <x:c r="D20" s="15"/>
+      <x:c r="E20" s="15"/>
+      <x:c r="F20" s="17"/>
+      <x:c r="G20" s="15"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="12"/>
-      <x:c r="B21" s="12"/>
-      <x:c r="C21" s="12"/>
-      <x:c r="D21" s="12"/>
-      <x:c r="E21" s="12"/>
-      <x:c r="F21" s="12"/>
-      <x:c r="G21" s="14"/>
-      <x:c r="H21" s="12"/>
+      <x:c r="A21" s="15"/>
+      <x:c r="B21" s="15"/>
+      <x:c r="C21" s="15"/>
+      <x:c r="D21" s="15"/>
+      <x:c r="E21" s="15"/>
+      <x:c r="F21" s="17"/>
+      <x:c r="G21" s="15"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="12"/>
-      <x:c r="B22" s="12"/>
-      <x:c r="C22" s="12"/>
-      <x:c r="D22" s="12"/>
-      <x:c r="E22" s="12"/>
-      <x:c r="F22" s="12"/>
-      <x:c r="G22" s="14"/>
-      <x:c r="H22" s="12"/>
+      <x:c r="A22" s="15"/>
+      <x:c r="B22" s="15"/>
+      <x:c r="C22" s="15"/>
+      <x:c r="D22" s="15"/>
+      <x:c r="E22" s="15"/>
+      <x:c r="F22" s="17"/>
+      <x:c r="G22" s="15"/>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="12"/>
-      <x:c r="B23" s="12"/>
-      <x:c r="C23" s="12"/>
-      <x:c r="D23" s="12"/>
-      <x:c r="E23" s="12"/>
-      <x:c r="F23" s="12"/>
-      <x:c r="G23" s="14"/>
-      <x:c r="H23" s="12"/>
+      <x:c r="A23" s="15"/>
+      <x:c r="B23" s="15"/>
+      <x:c r="C23" s="15"/>
+      <x:c r="D23" s="15"/>
+      <x:c r="E23" s="15"/>
+      <x:c r="F23" s="17"/>
+      <x:c r="G23" s="15"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="12"/>
-      <x:c r="B24" s="12"/>
-      <x:c r="C24" s="12"/>
-      <x:c r="D24" s="12"/>
-      <x:c r="E24" s="12"/>
-      <x:c r="F24" s="12"/>
-      <x:c r="G24" s="14"/>
-      <x:c r="H24" s="12"/>
+      <x:c r="A24" s="15"/>
+      <x:c r="B24" s="15"/>
+      <x:c r="C24" s="15"/>
+      <x:c r="D24" s="15"/>
+      <x:c r="E24" s="15"/>
+      <x:c r="F24" s="17"/>
+      <x:c r="G24" s="15"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="12"/>
-      <x:c r="B25" s="12"/>
-      <x:c r="C25" s="12"/>
-      <x:c r="D25" s="12"/>
-      <x:c r="E25" s="12"/>
-      <x:c r="F25" s="12"/>
-      <x:c r="G25" s="14"/>
-      <x:c r="H25" s="12"/>
+      <x:c r="A25" s="15"/>
+      <x:c r="B25" s="15"/>
+      <x:c r="C25" s="15"/>
+      <x:c r="D25" s="15"/>
+      <x:c r="E25" s="15"/>
+      <x:c r="F25" s="17"/>
+      <x:c r="G25" s="15"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="15"/>
+      <x:c r="B26" s="15"/>
+      <x:c r="C26" s="15"/>
+      <x:c r="D26" s="15"/>
+      <x:c r="E26" s="15"/>
+      <x:c r="F26" s="17"/>
+      <x:c r="G26" s="15"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="15"/>
+      <x:c r="B27" s="15"/>
+      <x:c r="C27" s="15"/>
+      <x:c r="D27" s="15"/>
+      <x:c r="E27" s="15"/>
+      <x:c r="F27" s="17"/>
+      <x:c r="G27" s="15"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="15"/>
+      <x:c r="B28" s="15"/>
+      <x:c r="C28" s="15"/>
+      <x:c r="D28" s="15"/>
+      <x:c r="E28" s="15"/>
+      <x:c r="F28" s="17"/>
+      <x:c r="G28" s="15"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="15"/>
+      <x:c r="B29" s="15"/>
+      <x:c r="C29" s="15"/>
+      <x:c r="D29" s="15"/>
+      <x:c r="E29" s="15"/>
+      <x:c r="F29" s="17"/>
+      <x:c r="G29" s="15"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="15"/>
+      <x:c r="B30" s="15"/>
+      <x:c r="C30" s="15"/>
+      <x:c r="D30" s="15"/>
+      <x:c r="E30" s="15"/>
+      <x:c r="F30" s="17"/>
+      <x:c r="G30" s="15"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="15"/>
+      <x:c r="B31" s="15"/>
+      <x:c r="C31" s="15"/>
+      <x:c r="D31" s="15"/>
+      <x:c r="E31" s="15"/>
+      <x:c r="F31" s="17"/>
+      <x:c r="G31" s="15"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="15"/>
+      <x:c r="B32" s="15"/>
+      <x:c r="C32" s="15"/>
+      <x:c r="D32" s="15"/>
+      <x:c r="E32" s="15"/>
+      <x:c r="F32" s="17"/>
+      <x:c r="G32" s="15"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="15"/>
+      <x:c r="B33" s="15"/>
+      <x:c r="C33" s="15"/>
+      <x:c r="D33" s="15"/>
+      <x:c r="E33" s="15"/>
+      <x:c r="F33" s="17"/>
+      <x:c r="G33" s="15"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="15"/>
+      <x:c r="B34" s="15"/>
+      <x:c r="C34" s="15"/>
+      <x:c r="D34" s="15"/>
+      <x:c r="E34" s="15"/>
+      <x:c r="F34" s="17"/>
+      <x:c r="G34" s="15"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="15"/>
+      <x:c r="B35" s="15"/>
+      <x:c r="C35" s="15"/>
+      <x:c r="D35" s="15"/>
+      <x:c r="E35" s="15"/>
+      <x:c r="F35" s="17"/>
+      <x:c r="G35" s="15"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="15"/>
+      <x:c r="B36" s="15"/>
+      <x:c r="C36" s="15"/>
+      <x:c r="D36" s="15"/>
+      <x:c r="E36" s="15"/>
+      <x:c r="F36" s="17"/>
+      <x:c r="G36" s="15"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="15"/>
+      <x:c r="B37" s="15"/>
+      <x:c r="C37" s="15"/>
+      <x:c r="D37" s="15"/>
+      <x:c r="E37" s="15"/>
+      <x:c r="F37" s="17"/>
+      <x:c r="G37" s="15"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="15"/>
+      <x:c r="B38" s="15"/>
+      <x:c r="C38" s="15"/>
+      <x:c r="D38" s="15"/>
+      <x:c r="E38" s="15"/>
+      <x:c r="F38" s="17"/>
+      <x:c r="G38" s="15"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="15"/>
+      <x:c r="B39" s="15"/>
+      <x:c r="C39" s="15"/>
+      <x:c r="D39" s="15"/>
+      <x:c r="E39" s="15"/>
+      <x:c r="F39" s="17"/>
+      <x:c r="G39" s="15"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="15"/>
+      <x:c r="B40" s="15"/>
+      <x:c r="C40" s="15"/>
+      <x:c r="D40" s="15"/>
+      <x:c r="E40" s="15"/>
+      <x:c r="F40" s="17"/>
+      <x:c r="G40" s="15"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="15"/>
+      <x:c r="B41" s="15"/>
+      <x:c r="C41" s="15"/>
+      <x:c r="D41" s="15"/>
+      <x:c r="E41" s="15"/>
+      <x:c r="F41" s="17"/>
+      <x:c r="G41" s="15"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="15"/>
+      <x:c r="B42" s="15"/>
+      <x:c r="C42" s="15"/>
+      <x:c r="D42" s="15"/>
+      <x:c r="E42" s="15"/>
+      <x:c r="F42" s="17"/>
+      <x:c r="G42" s="15"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="15"/>
+      <x:c r="B43" s="15"/>
+      <x:c r="C43" s="15"/>
+      <x:c r="D43" s="15"/>
+      <x:c r="E43" s="15"/>
+      <x:c r="F43" s="17"/>
+      <x:c r="G43" s="15"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="15"/>
+      <x:c r="B44" s="15"/>
+      <x:c r="C44" s="15"/>
+      <x:c r="D44" s="15"/>
+      <x:c r="E44" s="15"/>
+      <x:c r="F44" s="17"/>
+      <x:c r="G44" s="15"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="15"/>
+      <x:c r="B45" s="15"/>
+      <x:c r="C45" s="15"/>
+      <x:c r="D45" s="15"/>
+      <x:c r="E45" s="15"/>
+      <x:c r="F45" s="17"/>
+      <x:c r="G45" s="15"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="15"/>
+      <x:c r="B46" s="15"/>
+      <x:c r="C46" s="15"/>
+      <x:c r="D46" s="15"/>
+      <x:c r="E46" s="15"/>
+      <x:c r="F46" s="17"/>
+      <x:c r="G46" s="15"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="15"/>
+      <x:c r="B47" s="15"/>
+      <x:c r="C47" s="15"/>
+      <x:c r="D47" s="15"/>
+      <x:c r="E47" s="15"/>
+      <x:c r="F47" s="17"/>
+      <x:c r="G47" s="15"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="15"/>
+      <x:c r="B48" s="15"/>
+      <x:c r="C48" s="15"/>
+      <x:c r="D48" s="15"/>
+      <x:c r="E48" s="15"/>
+      <x:c r="F48" s="17"/>
+      <x:c r="G48" s="15"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="15"/>
+      <x:c r="B49" s="15"/>
+      <x:c r="C49" s="15"/>
+      <x:c r="D49" s="15"/>
+      <x:c r="E49" s="15"/>
+      <x:c r="F49" s="17"/>
+      <x:c r="G49" s="15"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="15"/>
+      <x:c r="B50" s="15"/>
+      <x:c r="C50" s="15"/>
+      <x:c r="D50" s="15"/>
+      <x:c r="E50" s="15"/>
+      <x:c r="F50" s="17"/>
+      <x:c r="G50" s="15"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="15"/>
+      <x:c r="B51" s="15"/>
+      <x:c r="C51" s="15"/>
+      <x:c r="D51" s="15"/>
+      <x:c r="E51" s="15"/>
+      <x:c r="F51" s="17"/>
+      <x:c r="G51" s="15"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="15"/>
+      <x:c r="B52" s="15"/>
+      <x:c r="C52" s="15"/>
+      <x:c r="D52" s="15"/>
+      <x:c r="E52" s="15"/>
+      <x:c r="F52" s="17"/>
+      <x:c r="G52" s="15"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="15"/>
+      <x:c r="B53" s="15"/>
+      <x:c r="C53" s="15"/>
+      <x:c r="D53" s="15"/>
+      <x:c r="E53" s="15"/>
+      <x:c r="F53" s="17"/>
+      <x:c r="G53" s="15"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="15"/>
+      <x:c r="B54" s="15"/>
+      <x:c r="C54" s="15"/>
+      <x:c r="D54" s="15"/>
+      <x:c r="E54" s="15"/>
+      <x:c r="F54" s="17"/>
+      <x:c r="G54" s="15"/>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="15"/>
+      <x:c r="B55" s="15"/>
+      <x:c r="C55" s="15"/>
+      <x:c r="D55" s="15"/>
+      <x:c r="E55" s="15"/>
+      <x:c r="F55" s="17"/>
+      <x:c r="G55" s="15"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="15"/>
+      <x:c r="B56" s="15"/>
+      <x:c r="C56" s="15"/>
+      <x:c r="D56" s="15"/>
+      <x:c r="E56" s="15"/>
+      <x:c r="F56" s="17"/>
+      <x:c r="G56" s="15"/>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="15"/>
+      <x:c r="B57" s="15"/>
+      <x:c r="C57" s="15"/>
+      <x:c r="D57" s="15"/>
+      <x:c r="E57" s="15"/>
+      <x:c r="F57" s="17"/>
+      <x:c r="G57" s="15"/>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="15"/>
+      <x:c r="B58" s="15"/>
+      <x:c r="C58" s="15"/>
+      <x:c r="D58" s="15"/>
+      <x:c r="E58" s="15"/>
+      <x:c r="F58" s="17"/>
+      <x:c r="G58" s="15"/>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="15"/>
+      <x:c r="B59" s="15"/>
+      <x:c r="C59" s="15"/>
+      <x:c r="D59" s="15"/>
+      <x:c r="E59" s="15"/>
+      <x:c r="F59" s="17"/>
+      <x:c r="G59" s="15"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="15"/>
+      <x:c r="B60" s="15"/>
+      <x:c r="C60" s="15"/>
+      <x:c r="D60" s="15"/>
+      <x:c r="E60" s="15"/>
+      <x:c r="F60" s="17"/>
+      <x:c r="G60" s="15"/>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="15"/>
+      <x:c r="B61" s="15"/>
+      <x:c r="C61" s="15"/>
+      <x:c r="D61" s="15"/>
+      <x:c r="E61" s="15"/>
+      <x:c r="F61" s="17"/>
+      <x:c r="G61" s="15"/>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="15"/>
+      <x:c r="B62" s="15"/>
+      <x:c r="C62" s="15"/>
+      <x:c r="D62" s="15"/>
+      <x:c r="E62" s="15"/>
+      <x:c r="F62" s="17"/>
+      <x:c r="G62" s="15"/>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="15"/>
+      <x:c r="B63" s="15"/>
+      <x:c r="C63" s="15"/>
+      <x:c r="D63" s="15"/>
+      <x:c r="E63" s="15"/>
+      <x:c r="F63" s="17"/>
+      <x:c r="G63" s="15"/>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="15"/>
+      <x:c r="B64" s="15"/>
+      <x:c r="C64" s="15"/>
+      <x:c r="D64" s="15"/>
+      <x:c r="E64" s="15"/>
+      <x:c r="F64" s="17"/>
+      <x:c r="G64" s="15"/>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="15"/>
+      <x:c r="B65" s="15"/>
+      <x:c r="C65" s="15"/>
+      <x:c r="D65" s="15"/>
+      <x:c r="E65" s="15"/>
+      <x:c r="F65" s="17"/>
+      <x:c r="G65" s="15"/>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="15"/>
+      <x:c r="B66" s="15"/>
+      <x:c r="C66" s="15"/>
+      <x:c r="D66" s="15"/>
+      <x:c r="E66" s="15"/>
+      <x:c r="F66" s="17"/>
+      <x:c r="G66" s="15"/>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="15"/>
+      <x:c r="B67" s="15"/>
+      <x:c r="C67" s="15"/>
+      <x:c r="D67" s="15"/>
+      <x:c r="E67" s="15"/>
+      <x:c r="F67" s="17"/>
+      <x:c r="G67" s="15"/>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" s="15"/>
+      <x:c r="B68" s="15"/>
+      <x:c r="C68" s="15"/>
+      <x:c r="D68" s="15"/>
+      <x:c r="E68" s="15"/>
+      <x:c r="F68" s="17"/>
+      <x:c r="G68" s="15"/>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" s="15"/>
+      <x:c r="B69" s="15"/>
+      <x:c r="C69" s="15"/>
+      <x:c r="D69" s="15"/>
+      <x:c r="E69" s="15"/>
+      <x:c r="F69" s="17"/>
+      <x:c r="G69" s="15"/>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" s="15"/>
+      <x:c r="B70" s="15"/>
+      <x:c r="C70" s="15"/>
+      <x:c r="D70" s="15"/>
+      <x:c r="E70" s="15"/>
+      <x:c r="F70" s="17"/>
+      <x:c r="G70" s="15"/>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" s="15"/>
+      <x:c r="B71" s="15"/>
+      <x:c r="C71" s="15"/>
+      <x:c r="D71" s="15"/>
+      <x:c r="E71" s="15"/>
+      <x:c r="F71" s="17"/>
+      <x:c r="G71" s="15"/>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" s="15"/>
+      <x:c r="B72" s="15"/>
+      <x:c r="C72" s="15"/>
+      <x:c r="D72" s="15"/>
+      <x:c r="E72" s="15"/>
+      <x:c r="F72" s="17"/>
+      <x:c r="G72" s="15"/>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" s="15"/>
+      <x:c r="B73" s="15"/>
+      <x:c r="C73" s="15"/>
+      <x:c r="D73" s="15"/>
+      <x:c r="E73" s="15"/>
+      <x:c r="F73" s="17"/>
+      <x:c r="G73" s="15"/>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" s="15"/>
+      <x:c r="B74" s="15"/>
+      <x:c r="C74" s="15"/>
+      <x:c r="D74" s="15"/>
+      <x:c r="E74" s="15"/>
+      <x:c r="F74" s="17"/>
+      <x:c r="G74" s="15"/>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" s="15"/>
+      <x:c r="B75" s="15"/>
+      <x:c r="C75" s="15"/>
+      <x:c r="D75" s="15"/>
+      <x:c r="E75" s="15"/>
+      <x:c r="F75" s="17"/>
+      <x:c r="G75" s="15"/>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" s="15"/>
+      <x:c r="B76" s="15"/>
+      <x:c r="C76" s="15"/>
+      <x:c r="D76" s="15"/>
+      <x:c r="E76" s="15"/>
+      <x:c r="F76" s="17"/>
+      <x:c r="G76" s="15"/>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" s="15"/>
+      <x:c r="B77" s="15"/>
+      <x:c r="C77" s="15"/>
+      <x:c r="D77" s="15"/>
+      <x:c r="E77" s="15"/>
+      <x:c r="F77" s="17"/>
+      <x:c r="G77" s="15"/>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" s="15"/>
+      <x:c r="B78" s="15"/>
+      <x:c r="C78" s="15"/>
+      <x:c r="D78" s="15"/>
+      <x:c r="E78" s="15"/>
+      <x:c r="F78" s="17"/>
+      <x:c r="G78" s="15"/>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" s="15"/>
+      <x:c r="B79" s="15"/>
+      <x:c r="C79" s="15"/>
+      <x:c r="D79" s="15"/>
+      <x:c r="E79" s="15"/>
+      <x:c r="F79" s="17"/>
+      <x:c r="G79" s="15"/>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" s="15"/>
+      <x:c r="B80" s="15"/>
+      <x:c r="C80" s="15"/>
+      <x:c r="D80" s="15"/>
+      <x:c r="E80" s="15"/>
+      <x:c r="F80" s="17"/>
+      <x:c r="G80" s="15"/>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" s="15"/>
+      <x:c r="B81" s="15"/>
+      <x:c r="C81" s="15"/>
+      <x:c r="D81" s="15"/>
+      <x:c r="E81" s="15"/>
+      <x:c r="F81" s="17"/>
+      <x:c r="G81" s="15"/>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" s="15"/>
+      <x:c r="B82" s="15"/>
+      <x:c r="C82" s="15"/>
+      <x:c r="D82" s="15"/>
+      <x:c r="E82" s="15"/>
+      <x:c r="F82" s="17"/>
+      <x:c r="G82" s="15"/>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" s="15"/>
+      <x:c r="B83" s="15"/>
+      <x:c r="C83" s="15"/>
+      <x:c r="D83" s="15"/>
+      <x:c r="E83" s="15"/>
+      <x:c r="F83" s="17"/>
+      <x:c r="G83" s="15"/>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" s="15"/>
+      <x:c r="B84" s="15"/>
+      <x:c r="C84" s="15"/>
+      <x:c r="D84" s="15"/>
+      <x:c r="E84" s="15"/>
+      <x:c r="F84" s="17"/>
+      <x:c r="G84" s="15"/>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" s="15"/>
+      <x:c r="B85" s="15"/>
+      <x:c r="C85" s="15"/>
+      <x:c r="D85" s="15"/>
+      <x:c r="E85" s="15"/>
+      <x:c r="F85" s="17"/>
+      <x:c r="G85" s="15"/>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" s="15"/>
+      <x:c r="B86" s="15"/>
+      <x:c r="C86" s="15"/>
+      <x:c r="D86" s="15"/>
+      <x:c r="E86" s="15"/>
+      <x:c r="F86" s="17"/>
+      <x:c r="G86" s="15"/>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" s="15"/>
+      <x:c r="B87" s="15"/>
+      <x:c r="C87" s="15"/>
+      <x:c r="D87" s="15"/>
+      <x:c r="E87" s="15"/>
+      <x:c r="F87" s="17"/>
+      <x:c r="G87" s="15"/>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" s="15"/>
+      <x:c r="B88" s="15"/>
+      <x:c r="C88" s="15"/>
+      <x:c r="D88" s="15"/>
+      <x:c r="E88" s="15"/>
+      <x:c r="F88" s="17"/>
+      <x:c r="G88" s="15"/>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" s="15"/>
+      <x:c r="B89" s="15"/>
+      <x:c r="C89" s="15"/>
+      <x:c r="D89" s="15"/>
+      <x:c r="E89" s="15"/>
+      <x:c r="F89" s="17"/>
+      <x:c r="G89" s="15"/>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" s="15"/>
+      <x:c r="B90" s="15"/>
+      <x:c r="C90" s="15"/>
+      <x:c r="D90" s="15"/>
+      <x:c r="E90" s="15"/>
+      <x:c r="F90" s="17"/>
+      <x:c r="G90" s="15"/>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" s="15"/>
+      <x:c r="B91" s="15"/>
+      <x:c r="C91" s="15"/>
+      <x:c r="D91" s="15"/>
+      <x:c r="E91" s="15"/>
+      <x:c r="F91" s="17"/>
+      <x:c r="G91" s="15"/>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" s="15"/>
+      <x:c r="B92" s="15"/>
+      <x:c r="C92" s="15"/>
+      <x:c r="D92" s="15"/>
+      <x:c r="E92" s="15"/>
+      <x:c r="F92" s="17"/>
+      <x:c r="G92" s="15"/>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" s="15"/>
+      <x:c r="B93" s="15"/>
+      <x:c r="C93" s="15"/>
+      <x:c r="D93" s="15"/>
+      <x:c r="E93" s="15"/>
+      <x:c r="F93" s="17"/>
+      <x:c r="G93" s="15"/>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" s="15"/>
+      <x:c r="B94" s="15"/>
+      <x:c r="C94" s="15"/>
+      <x:c r="D94" s="15"/>
+      <x:c r="E94" s="15"/>
+      <x:c r="F94" s="17"/>
+      <x:c r="G94" s="15"/>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" s="15"/>
+      <x:c r="B95" s="15"/>
+      <x:c r="C95" s="15"/>
+      <x:c r="D95" s="15"/>
+      <x:c r="E95" s="15"/>
+      <x:c r="F95" s="17"/>
+      <x:c r="G95" s="15"/>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" s="15"/>
+      <x:c r="B96" s="15"/>
+      <x:c r="C96" s="15"/>
+      <x:c r="D96" s="15"/>
+      <x:c r="E96" s="15"/>
+      <x:c r="F96" s="17"/>
+      <x:c r="G96" s="15"/>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" s="15"/>
+      <x:c r="B97" s="15"/>
+      <x:c r="C97" s="15"/>
+      <x:c r="D97" s="15"/>
+      <x:c r="E97" s="15"/>
+      <x:c r="F97" s="17"/>
+      <x:c r="G97" s="15"/>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" s="15"/>
+      <x:c r="B98" s="15"/>
+      <x:c r="C98" s="15"/>
+      <x:c r="D98" s="15"/>
+      <x:c r="E98" s="15"/>
+      <x:c r="F98" s="17"/>
+      <x:c r="G98" s="15"/>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" s="15"/>
+      <x:c r="B99" s="15"/>
+      <x:c r="C99" s="15"/>
+      <x:c r="D99" s="15"/>
+      <x:c r="E99" s="15"/>
+      <x:c r="F99" s="17"/>
+      <x:c r="G99" s="15"/>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" s="15"/>
+      <x:c r="B100" s="15"/>
+      <x:c r="C100" s="15"/>
+      <x:c r="D100" s="15"/>
+      <x:c r="E100" s="15"/>
+      <x:c r="F100" s="17"/>
+      <x:c r="G100" s="15"/>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" s="15"/>
+      <x:c r="B101" s="15"/>
+      <x:c r="C101" s="15"/>
+      <x:c r="D101" s="15"/>
+      <x:c r="E101" s="15"/>
+      <x:c r="F101" s="17"/>
+      <x:c r="G101" s="15"/>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" s="15"/>
+      <x:c r="B102" s="15"/>
+      <x:c r="C102" s="15"/>
+      <x:c r="D102" s="15"/>
+      <x:c r="E102" s="15"/>
+      <x:c r="F102" s="17"/>
+      <x:c r="G102" s="15"/>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" s="15"/>
+      <x:c r="B103" s="15"/>
+      <x:c r="C103" s="15"/>
+      <x:c r="D103" s="15"/>
+      <x:c r="E103" s="15"/>
+      <x:c r="F103" s="17"/>
+      <x:c r="G103" s="15"/>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" s="15"/>
+      <x:c r="B104" s="15"/>
+      <x:c r="C104" s="15"/>
+      <x:c r="D104" s="15"/>
+      <x:c r="E104" s="15"/>
+      <x:c r="F104" s="17"/>
+      <x:c r="G104" s="15"/>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" s="15"/>
+      <x:c r="B105" s="15"/>
+      <x:c r="C105" s="15"/>
+      <x:c r="D105" s="15"/>
+      <x:c r="E105" s="15"/>
+      <x:c r="F105" s="17"/>
+      <x:c r="G105" s="15"/>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" s="15"/>
+      <x:c r="B106" s="15"/>
+      <x:c r="C106" s="15"/>
+      <x:c r="D106" s="15"/>
+      <x:c r="E106" s="15"/>
+      <x:c r="F106" s="17"/>
+      <x:c r="G106" s="15"/>
+    </x:row>
+    <x:row r="107">
+      <x:c r="A107" s="15"/>
+      <x:c r="B107" s="15"/>
+      <x:c r="C107" s="15"/>
+      <x:c r="D107" s="15"/>
+      <x:c r="E107" s="15"/>
+      <x:c r="F107" s="17"/>
+      <x:c r="G107" s="15"/>
+    </x:row>
+    <x:row r="108">
+      <x:c r="A108" s="15"/>
+      <x:c r="B108" s="15"/>
+      <x:c r="C108" s="15"/>
+      <x:c r="D108" s="15"/>
+      <x:c r="E108" s="15"/>
+      <x:c r="F108" s="17"/>
+      <x:c r="G108" s="15"/>
+    </x:row>
+    <x:row r="109">
+      <x:c r="A109" s="15"/>
+      <x:c r="B109" s="15"/>
+      <x:c r="C109" s="15"/>
+      <x:c r="D109" s="15"/>
+      <x:c r="E109" s="15"/>
+      <x:c r="F109" s="17"/>
+      <x:c r="G109" s="15"/>
+    </x:row>
+    <x:row r="110">
+      <x:c r="A110" s="15"/>
+      <x:c r="B110" s="15"/>
+      <x:c r="C110" s="15"/>
+      <x:c r="D110" s="15"/>
+      <x:c r="E110" s="15"/>
+      <x:c r="F110" s="17"/>
+      <x:c r="G110" s="15"/>
+    </x:row>
+    <x:row r="111">
+      <x:c r="A111" s="15"/>
+      <x:c r="B111" s="15"/>
+      <x:c r="C111" s="15"/>
+      <x:c r="D111" s="15"/>
+      <x:c r="E111" s="15"/>
+      <x:c r="F111" s="17"/>
+      <x:c r="G111" s="15"/>
+    </x:row>
+    <x:row r="112">
+      <x:c r="A112" s="15"/>
+      <x:c r="B112" s="15"/>
+      <x:c r="C112" s="15"/>
+      <x:c r="D112" s="15"/>
+      <x:c r="E112" s="15"/>
+      <x:c r="F112" s="17"/>
+      <x:c r="G112" s="15"/>
+    </x:row>
+    <x:row r="113">
+      <x:c r="A113" s="15"/>
+      <x:c r="B113" s="15"/>
+      <x:c r="C113" s="15"/>
+      <x:c r="D113" s="15"/>
+      <x:c r="E113" s="15"/>
+      <x:c r="F113" s="17"/>
+      <x:c r="G113" s="15"/>
+    </x:row>
+    <x:row r="114">
+      <x:c r="A114" s="15"/>
+      <x:c r="B114" s="15"/>
+      <x:c r="C114" s="15"/>
+      <x:c r="D114" s="15"/>
+      <x:c r="E114" s="15"/>
+      <x:c r="F114" s="17"/>
+      <x:c r="G114" s="15"/>
+    </x:row>
+    <x:row r="115">
+      <x:c r="A115" s="15"/>
+      <x:c r="B115" s="15"/>
+      <x:c r="C115" s="15"/>
+      <x:c r="D115" s="15"/>
+      <x:c r="E115" s="15"/>
+      <x:c r="F115" s="17"/>
+      <x:c r="G115" s="15"/>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116" s="15"/>
+      <x:c r="B116" s="15"/>
+      <x:c r="C116" s="15"/>
+      <x:c r="D116" s="15"/>
+      <x:c r="E116" s="15"/>
+      <x:c r="F116" s="17"/>
+      <x:c r="G116" s="15"/>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117" s="15"/>
+      <x:c r="B117" s="15"/>
+      <x:c r="C117" s="15"/>
+      <x:c r="D117" s="15"/>
+      <x:c r="E117" s="15"/>
+      <x:c r="F117" s="17"/>
+      <x:c r="G117" s="15"/>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118" s="15"/>
+      <x:c r="B118" s="15"/>
+      <x:c r="C118" s="15"/>
+      <x:c r="D118" s="15"/>
+      <x:c r="E118" s="15"/>
+      <x:c r="F118" s="17"/>
+      <x:c r="G118" s="15"/>
+    </x:row>
+    <x:row r="119">
+      <x:c r="A119" s="15"/>
+      <x:c r="B119" s="15"/>
+      <x:c r="C119" s="15"/>
+      <x:c r="D119" s="15"/>
+      <x:c r="E119" s="15"/>
+      <x:c r="F119" s="17"/>
+      <x:c r="G119" s="15"/>
+    </x:row>
+    <x:row r="120">
+      <x:c r="A120" s="15"/>
+      <x:c r="B120" s="15"/>
+      <x:c r="C120" s="15"/>
+      <x:c r="D120" s="15"/>
+      <x:c r="E120" s="15"/>
+      <x:c r="F120" s="17"/>
+      <x:c r="G120" s="15"/>
+    </x:row>
+    <x:row r="121">
+      <x:c r="A121" s="15"/>
+      <x:c r="B121" s="15"/>
+      <x:c r="C121" s="15"/>
+      <x:c r="D121" s="15"/>
+      <x:c r="E121" s="15"/>
+      <x:c r="F121" s="17"/>
+      <x:c r="G121" s="15"/>
+    </x:row>
+    <x:row r="122">
+      <x:c r="A122" s="15"/>
+      <x:c r="B122" s="15"/>
+      <x:c r="C122" s="15"/>
+      <x:c r="D122" s="15"/>
+      <x:c r="E122" s="15"/>
+      <x:c r="F122" s="17"/>
+      <x:c r="G122" s="15"/>
+    </x:row>
+    <x:row r="123">
+      <x:c r="A123" s="15"/>
+      <x:c r="B123" s="15"/>
+      <x:c r="C123" s="15"/>
+      <x:c r="D123" s="15"/>
+      <x:c r="E123" s="15"/>
+      <x:c r="F123" s="17"/>
+      <x:c r="G123" s="15"/>
+    </x:row>
+    <x:row r="124">
+      <x:c r="A124" s="15"/>
+      <x:c r="B124" s="15"/>
+      <x:c r="C124" s="15"/>
+      <x:c r="D124" s="15"/>
+      <x:c r="E124" s="15"/>
+      <x:c r="F124" s="17"/>
+      <x:c r="G124" s="15"/>
+    </x:row>
+    <x:row r="125">
+      <x:c r="A125" s="15"/>
+      <x:c r="B125" s="15"/>
+      <x:c r="C125" s="15"/>
+      <x:c r="D125" s="15"/>
+      <x:c r="E125" s="15"/>
+      <x:c r="F125" s="17"/>
+      <x:c r="G125" s="15"/>
+    </x:row>
+    <x:row r="126">
+      <x:c r="A126" s="15"/>
+      <x:c r="B126" s="15"/>
+      <x:c r="C126" s="15"/>
+      <x:c r="D126" s="15"/>
+      <x:c r="E126" s="15"/>
+      <x:c r="F126" s="17"/>
+      <x:c r="G126" s="15"/>
+    </x:row>
+    <x:row r="127">
+      <x:c r="A127" s="15"/>
+      <x:c r="B127" s="15"/>
+      <x:c r="C127" s="15"/>
+      <x:c r="D127" s="15"/>
+      <x:c r="E127" s="15"/>
+      <x:c r="F127" s="17"/>
+      <x:c r="G127" s="15"/>
+    </x:row>
+    <x:row r="128">
+      <x:c r="A128" s="15"/>
+      <x:c r="B128" s="15"/>
+      <x:c r="C128" s="15"/>
+      <x:c r="D128" s="15"/>
+      <x:c r="E128" s="15"/>
+      <x:c r="F128" s="17"/>
+      <x:c r="G128" s="15"/>
+    </x:row>
+    <x:row r="129">
+      <x:c r="A129" s="15"/>
+      <x:c r="B129" s="15"/>
+      <x:c r="C129" s="15"/>
+      <x:c r="D129" s="15"/>
+      <x:c r="E129" s="15"/>
+      <x:c r="F129" s="17"/>
+      <x:c r="G129" s="15"/>
+    </x:row>
+    <x:row r="130">
+      <x:c r="A130" s="15"/>
+      <x:c r="B130" s="15"/>
+      <x:c r="C130" s="15"/>
+      <x:c r="D130" s="15"/>
+      <x:c r="E130" s="15"/>
+      <x:c r="F130" s="17"/>
+      <x:c r="G130" s="15"/>
+    </x:row>
+    <x:row r="131">
+      <x:c r="A131" s="15"/>
+      <x:c r="B131" s="15"/>
+      <x:c r="C131" s="15"/>
+      <x:c r="D131" s="15"/>
+      <x:c r="E131" s="15"/>
+      <x:c r="F131" s="17"/>
+      <x:c r="G131" s="15"/>
+    </x:row>
+    <x:row r="132">
+      <x:c r="A132" s="15"/>
+      <x:c r="B132" s="15"/>
+      <x:c r="C132" s="15"/>
+      <x:c r="D132" s="15"/>
+      <x:c r="E132" s="15"/>
+      <x:c r="F132" s="17"/>
+      <x:c r="G132" s="15"/>
+    </x:row>
+    <x:row r="133">
+      <x:c r="A133" s="15"/>
+      <x:c r="B133" s="15"/>
+      <x:c r="C133" s="15"/>
+      <x:c r="D133" s="15"/>
+      <x:c r="E133" s="15"/>
+      <x:c r="F133" s="17"/>
+      <x:c r="G133" s="15"/>
+    </x:row>
+    <x:row r="134">
+      <x:c r="A134" s="15"/>
+      <x:c r="B134" s="15"/>
+      <x:c r="C134" s="15"/>
+      <x:c r="D134" s="15"/>
+      <x:c r="E134" s="15"/>
+      <x:c r="F134" s="17"/>
+      <x:c r="G134" s="15"/>
+    </x:row>
+    <x:row r="135">
+      <x:c r="A135" s="15"/>
+      <x:c r="B135" s="15"/>
+      <x:c r="C135" s="15"/>
+      <x:c r="D135" s="15"/>
+      <x:c r="E135" s="15"/>
+      <x:c r="F135" s="17"/>
+      <x:c r="G135" s="15"/>
+    </x:row>
+    <x:row r="136">
+      <x:c r="A136" s="15"/>
+      <x:c r="B136" s="15"/>
+      <x:c r="C136" s="15"/>
+      <x:c r="D136" s="15"/>
+      <x:c r="E136" s="15"/>
+      <x:c r="F136" s="17"/>
+      <x:c r="G136" s="15"/>
+    </x:row>
+    <x:row r="137">
+      <x:c r="A137" s="15"/>
+      <x:c r="B137" s="15"/>
+      <x:c r="C137" s="15"/>
+      <x:c r="D137" s="15"/>
+      <x:c r="E137" s="15"/>
+      <x:c r="F137" s="17"/>
+      <x:c r="G137" s="15"/>
+    </x:row>
+    <x:row r="138">
+      <x:c r="A138" s="15"/>
+      <x:c r="B138" s="15"/>
+      <x:c r="C138" s="15"/>
+      <x:c r="D138" s="15"/>
+      <x:c r="E138" s="15"/>
+      <x:c r="F138" s="17"/>
+      <x:c r="G138" s="15"/>
+    </x:row>
+    <x:row r="139">
+      <x:c r="A139" s="15"/>
+      <x:c r="B139" s="15"/>
+      <x:c r="C139" s="15"/>
+      <x:c r="D139" s="15"/>
+      <x:c r="E139" s="15"/>
+      <x:c r="F139" s="17"/>
+      <x:c r="G139" s="15"/>
+    </x:row>
+    <x:row r="140">
+      <x:c r="A140" s="15"/>
+      <x:c r="B140" s="15"/>
+      <x:c r="C140" s="15"/>
+      <x:c r="D140" s="15"/>
+      <x:c r="E140" s="15"/>
+      <x:c r="F140" s="17"/>
+      <x:c r="G140" s="15"/>
+    </x:row>
+    <x:row r="141">
+      <x:c r="A141" s="15"/>
+      <x:c r="B141" s="15"/>
+      <x:c r="C141" s="15"/>
+      <x:c r="D141" s="15"/>
+      <x:c r="E141" s="15"/>
+      <x:c r="F141" s="17"/>
+      <x:c r="G141" s="15"/>
+    </x:row>
+    <x:row r="142">
+      <x:c r="A142" s="15"/>
+      <x:c r="B142" s="15"/>
+      <x:c r="C142" s="15"/>
+      <x:c r="D142" s="15"/>
+      <x:c r="E142" s="15"/>
+      <x:c r="F142" s="17"/>
+      <x:c r="G142" s="15"/>
+    </x:row>
+    <x:row r="143">
+      <x:c r="A143" s="15"/>
+      <x:c r="B143" s="15"/>
+      <x:c r="C143" s="15"/>
+      <x:c r="D143" s="15"/>
+      <x:c r="E143" s="15"/>
+      <x:c r="F143" s="17"/>
+      <x:c r="G143" s="15"/>
+    </x:row>
+    <x:row r="144">
+      <x:c r="A144" s="15"/>
+      <x:c r="B144" s="15"/>
+      <x:c r="C144" s="15"/>
+      <x:c r="D144" s="15"/>
+      <x:c r="E144" s="15"/>
+      <x:c r="F144" s="17"/>
+      <x:c r="G144" s="15"/>
+    </x:row>
+    <x:row r="145">
+      <x:c r="A145" s="15"/>
+      <x:c r="B145" s="15"/>
+      <x:c r="C145" s="15"/>
+      <x:c r="D145" s="15"/>
+      <x:c r="E145" s="15"/>
+      <x:c r="F145" s="17"/>
+      <x:c r="G145" s="15"/>
+    </x:row>
+    <x:row r="146">
+      <x:c r="A146" s="15"/>
+      <x:c r="B146" s="15"/>
+      <x:c r="C146" s="15"/>
+      <x:c r="D146" s="15"/>
+      <x:c r="E146" s="15"/>
+      <x:c r="F146" s="17"/>
+      <x:c r="G146" s="15"/>
+    </x:row>
+    <x:row r="147">
+      <x:c r="A147" s="15"/>
+      <x:c r="B147" s="15"/>
+      <x:c r="C147" s="15"/>
+      <x:c r="D147" s="15"/>
+      <x:c r="E147" s="15"/>
+      <x:c r="F147" s="17"/>
+      <x:c r="G147" s="15"/>
+    </x:row>
+    <x:row r="148">
+      <x:c r="A148" s="15"/>
+      <x:c r="B148" s="15"/>
+      <x:c r="C148" s="15"/>
+      <x:c r="D148" s="15"/>
+      <x:c r="E148" s="15"/>
+      <x:c r="F148" s="17"/>
+      <x:c r="G148" s="15"/>
+    </x:row>
+    <x:row r="149">
+      <x:c r="A149" s="15"/>
+      <x:c r="B149" s="15"/>
+      <x:c r="C149" s="15"/>
+      <x:c r="D149" s="15"/>
+      <x:c r="E149" s="15"/>
+      <x:c r="F149" s="17"/>
+      <x:c r="G149" s="15"/>
+    </x:row>
+    <x:row r="150">
+      <x:c r="A150" s="15"/>
+      <x:c r="B150" s="15"/>
+      <x:c r="C150" s="15"/>
+      <x:c r="D150" s="15"/>
+      <x:c r="E150" s="15"/>
+      <x:c r="F150" s="17"/>
+      <x:c r="G150" s="15"/>
+    </x:row>
+    <x:row r="151">
+      <x:c r="A151" s="15"/>
+      <x:c r="B151" s="15"/>
+      <x:c r="C151" s="15"/>
+      <x:c r="D151" s="15"/>
+      <x:c r="E151" s="15"/>
+      <x:c r="F151" s="17"/>
+      <x:c r="G151" s="15"/>
+    </x:row>
+    <x:row r="152">
+      <x:c r="A152" s="15"/>
+      <x:c r="B152" s="15"/>
+      <x:c r="C152" s="15"/>
+      <x:c r="D152" s="15"/>
+      <x:c r="E152" s="15"/>
+      <x:c r="F152" s="17"/>
+      <x:c r="G152" s="15"/>
+    </x:row>
+    <x:row r="153">
+      <x:c r="A153" s="15"/>
+      <x:c r="B153" s="15"/>
+      <x:c r="C153" s="15"/>
+      <x:c r="D153" s="15"/>
+      <x:c r="E153" s="15"/>
+      <x:c r="F153" s="17"/>
+      <x:c r="G153" s="15"/>
+    </x:row>
+    <x:row r="154">
+      <x:c r="A154" s="15"/>
+      <x:c r="B154" s="15"/>
+      <x:c r="C154" s="15"/>
+      <x:c r="D154" s="15"/>
+      <x:c r="E154" s="15"/>
+      <x:c r="F154" s="17"/>
+      <x:c r="G154" s="15"/>
+    </x:row>
+    <x:row r="155">
+      <x:c r="A155" s="15"/>
+      <x:c r="B155" s="15"/>
+      <x:c r="C155" s="15"/>
+      <x:c r="D155" s="15"/>
+      <x:c r="E155" s="15"/>
+      <x:c r="F155" s="17"/>
+      <x:c r="G155" s="15"/>
+    </x:row>
+    <x:row r="156">
+      <x:c r="A156" s="15"/>
+      <x:c r="B156" s="15"/>
+      <x:c r="C156" s="15"/>
+      <x:c r="D156" s="15"/>
+      <x:c r="E156" s="15"/>
+      <x:c r="F156" s="17"/>
+      <x:c r="G156" s="15"/>
+    </x:row>
+    <x:row r="157">
+      <x:c r="A157" s="15"/>
+      <x:c r="B157" s="15"/>
+      <x:c r="C157" s="15"/>
+      <x:c r="D157" s="15"/>
+      <x:c r="E157" s="15"/>
+      <x:c r="F157" s="17"/>
+      <x:c r="G157" s="15"/>
+    </x:row>
+    <x:row r="158">
+      <x:c r="A158" s="15"/>
+      <x:c r="B158" s="15"/>
+      <x:c r="C158" s="15"/>
+      <x:c r="D158" s="15"/>
+      <x:c r="E158" s="15"/>
+      <x:c r="F158" s="17"/>
+      <x:c r="G158" s="15"/>
+    </x:row>
+    <x:row r="159">
+      <x:c r="A159" s="15"/>
+      <x:c r="B159" s="15"/>
+      <x:c r="C159" s="15"/>
+      <x:c r="D159" s="15"/>
+      <x:c r="E159" s="15"/>
+      <x:c r="F159" s="17"/>
+      <x:c r="G159" s="15"/>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160" s="15"/>
+      <x:c r="B160" s="15"/>
+      <x:c r="C160" s="15"/>
+      <x:c r="D160" s="15"/>
+      <x:c r="E160" s="15"/>
+      <x:c r="F160" s="17"/>
+      <x:c r="G160" s="15"/>
+    </x:row>
+    <x:row r="161">
+      <x:c r="A161" s="15"/>
+      <x:c r="B161" s="15"/>
+      <x:c r="C161" s="15"/>
+      <x:c r="D161" s="15"/>
+      <x:c r="E161" s="15"/>
+      <x:c r="F161" s="17"/>
+      <x:c r="G161" s="15"/>
+    </x:row>
+    <x:row r="162">
+      <x:c r="A162" s="15"/>
+      <x:c r="B162" s="15"/>
+      <x:c r="C162" s="15"/>
+      <x:c r="D162" s="15"/>
+      <x:c r="E162" s="15"/>
+      <x:c r="F162" s="17"/>
+      <x:c r="G162" s="15"/>
+    </x:row>
+    <x:row r="163">
+      <x:c r="A163" s="15"/>
+      <x:c r="B163" s="15"/>
+      <x:c r="C163" s="15"/>
+      <x:c r="D163" s="15"/>
+      <x:c r="E163" s="15"/>
+      <x:c r="F163" s="17"/>
+      <x:c r="G163" s="15"/>
+    </x:row>
+    <x:row r="164">
+      <x:c r="A164" s="15"/>
+      <x:c r="B164" s="15"/>
+      <x:c r="C164" s="15"/>
+      <x:c r="D164" s="15"/>
+      <x:c r="E164" s="15"/>
+      <x:c r="F164" s="17"/>
+      <x:c r="G164" s="15"/>
+    </x:row>
+    <x:row r="165">
+      <x:c r="A165" s="15"/>
+      <x:c r="B165" s="15"/>
+      <x:c r="C165" s="15"/>
+      <x:c r="D165" s="15"/>
+      <x:c r="E165" s="15"/>
+      <x:c r="F165" s="17"/>
+      <x:c r="G165" s="15"/>
+    </x:row>
+    <x:row r="166">
+      <x:c r="A166" s="15"/>
+      <x:c r="B166" s="15"/>
+      <x:c r="C166" s="15"/>
+      <x:c r="D166" s="15"/>
+      <x:c r="E166" s="15"/>
+      <x:c r="F166" s="17"/>
+      <x:c r="G166" s="15"/>
+    </x:row>
+    <x:row r="167">
+      <x:c r="A167" s="15"/>
+      <x:c r="B167" s="15"/>
+      <x:c r="C167" s="15"/>
+      <x:c r="D167" s="15"/>
+      <x:c r="E167" s="15"/>
+      <x:c r="F167" s="17"/>
+      <x:c r="G167" s="15"/>
+    </x:row>
+    <x:row r="168">
+      <x:c r="A168" s="15"/>
+      <x:c r="B168" s="15"/>
+      <x:c r="C168" s="15"/>
+      <x:c r="D168" s="15"/>
+      <x:c r="E168" s="15"/>
+      <x:c r="F168" s="17"/>
+      <x:c r="G168" s="15"/>
+    </x:row>
+    <x:row r="169">
+      <x:c r="A169" s="15"/>
+      <x:c r="B169" s="15"/>
+      <x:c r="C169" s="15"/>
+      <x:c r="D169" s="15"/>
+      <x:c r="E169" s="15"/>
+      <x:c r="F169" s="17"/>
+      <x:c r="G169" s="15"/>
+    </x:row>
+    <x:row r="170">
+      <x:c r="A170" s="15"/>
+      <x:c r="B170" s="15"/>
+      <x:c r="C170" s="15"/>
+      <x:c r="D170" s="15"/>
+      <x:c r="E170" s="15"/>
+      <x:c r="F170" s="17"/>
+      <x:c r="G170" s="15"/>
+    </x:row>
+    <x:row r="171">
+      <x:c r="A171" s="15"/>
+      <x:c r="B171" s="15"/>
+      <x:c r="C171" s="15"/>
+      <x:c r="D171" s="15"/>
+      <x:c r="E171" s="15"/>
+      <x:c r="F171" s="17"/>
+      <x:c r="G171" s="15"/>
+    </x:row>
+    <x:row r="172">
+      <x:c r="A172" s="15"/>
+      <x:c r="B172" s="15"/>
+      <x:c r="C172" s="15"/>
+      <x:c r="D172" s="15"/>
+      <x:c r="E172" s="15"/>
+      <x:c r="F172" s="17"/>
+      <x:c r="G172" s="15"/>
+    </x:row>
+    <x:row r="173">
+      <x:c r="A173" s="15"/>
+      <x:c r="B173" s="15"/>
+      <x:c r="C173" s="15"/>
+      <x:c r="D173" s="15"/>
+      <x:c r="E173" s="15"/>
+      <x:c r="F173" s="17"/>
+      <x:c r="G173" s="15"/>
+    </x:row>
+    <x:row r="174">
+      <x:c r="A174" s="15"/>
+      <x:c r="B174" s="15"/>
+      <x:c r="C174" s="15"/>
+      <x:c r="D174" s="15"/>
+      <x:c r="E174" s="15"/>
+      <x:c r="F174" s="17"/>
+      <x:c r="G174" s="15"/>
+    </x:row>
+    <x:row r="175">
+      <x:c r="A175" s="15"/>
+      <x:c r="B175" s="15"/>
+      <x:c r="C175" s="15"/>
+      <x:c r="D175" s="15"/>
+      <x:c r="E175" s="15"/>
+      <x:c r="F175" s="17"/>
+      <x:c r="G175" s="15"/>
+    </x:row>
+    <x:row r="176">
+      <x:c r="A176" s="15"/>
+      <x:c r="B176" s="15"/>
+      <x:c r="C176" s="15"/>
+      <x:c r="D176" s="15"/>
+      <x:c r="E176" s="15"/>
+      <x:c r="F176" s="17"/>
+      <x:c r="G176" s="15"/>
+    </x:row>
+    <x:row r="177">
+      <x:c r="A177" s="15"/>
+      <x:c r="B177" s="15"/>
+      <x:c r="C177" s="15"/>
+      <x:c r="D177" s="15"/>
+      <x:c r="E177" s="15"/>
+      <x:c r="F177" s="17"/>
+      <x:c r="G177" s="15"/>
+    </x:row>
+    <x:row r="178">
+      <x:c r="A178" s="15"/>
+      <x:c r="B178" s="15"/>
+      <x:c r="C178" s="15"/>
+      <x:c r="D178" s="15"/>
+      <x:c r="E178" s="15"/>
+      <x:c r="F178" s="17"/>
+      <x:c r="G178" s="15"/>
+    </x:row>
+    <x:row r="179">
+      <x:c r="A179" s="15"/>
+      <x:c r="B179" s="15"/>
+      <x:c r="C179" s="15"/>
+      <x:c r="D179" s="15"/>
+      <x:c r="E179" s="15"/>
+      <x:c r="F179" s="17"/>
+      <x:c r="G179" s="15"/>
+    </x:row>
+    <x:row r="180">
+      <x:c r="A180" s="15"/>
+      <x:c r="B180" s="15"/>
+      <x:c r="C180" s="15"/>
+      <x:c r="D180" s="15"/>
+      <x:c r="E180" s="15"/>
+      <x:c r="F180" s="17"/>
+      <x:c r="G180" s="15"/>
+    </x:row>
+    <x:row r="181">
+      <x:c r="A181" s="15"/>
+      <x:c r="B181" s="15"/>
+      <x:c r="C181" s="15"/>
+      <x:c r="D181" s="15"/>
+      <x:c r="E181" s="15"/>
+      <x:c r="F181" s="17"/>
+      <x:c r="G181" s="15"/>
+    </x:row>
+    <x:row r="182">
+      <x:c r="A182" s="15"/>
+      <x:c r="B182" s="15"/>
+      <x:c r="C182" s="15"/>
+      <x:c r="D182" s="15"/>
+      <x:c r="E182" s="15"/>
+      <x:c r="F182" s="17"/>
+      <x:c r="G182" s="15"/>
+    </x:row>
+    <x:row r="183">
+      <x:c r="A183" s="15"/>
+      <x:c r="B183" s="15"/>
+      <x:c r="C183" s="15"/>
+      <x:c r="D183" s="15"/>
+      <x:c r="E183" s="15"/>
+      <x:c r="F183" s="17"/>
+      <x:c r="G183" s="15"/>
+    </x:row>
+    <x:row r="184">
+      <x:c r="A184" s="15"/>
+      <x:c r="B184" s="15"/>
+      <x:c r="C184" s="15"/>
+      <x:c r="D184" s="15"/>
+      <x:c r="E184" s="15"/>
+      <x:c r="F184" s="17"/>
+      <x:c r="G184" s="15"/>
+    </x:row>
+    <x:row r="185">
+      <x:c r="A185" s="15"/>
+      <x:c r="B185" s="15"/>
+      <x:c r="C185" s="15"/>
+      <x:c r="D185" s="15"/>
+      <x:c r="E185" s="15"/>
+      <x:c r="F185" s="17"/>
+      <x:c r="G185" s="15"/>
+    </x:row>
+    <x:row r="186">
+      <x:c r="A186" s="15"/>
+      <x:c r="B186" s="15"/>
+      <x:c r="C186" s="15"/>
+      <x:c r="D186" s="15"/>
+      <x:c r="E186" s="15"/>
+      <x:c r="F186" s="17"/>
+      <x:c r="G186" s="15"/>
+    </x:row>
+    <x:row r="187">
+      <x:c r="A187" s="15"/>
+      <x:c r="B187" s="15"/>
+      <x:c r="C187" s="15"/>
+      <x:c r="D187" s="15"/>
+      <x:c r="E187" s="15"/>
+      <x:c r="F187" s="17"/>
+      <x:c r="G187" s="15"/>
+    </x:row>
+    <x:row r="188">
+      <x:c r="A188" s="15"/>
+      <x:c r="B188" s="15"/>
+      <x:c r="C188" s="15"/>
+      <x:c r="D188" s="15"/>
+      <x:c r="E188" s="15"/>
+      <x:c r="F188" s="17"/>
+      <x:c r="G188" s="15"/>
+    </x:row>
+    <x:row r="189">
+      <x:c r="A189" s="15"/>
+      <x:c r="B189" s="15"/>
+      <x:c r="C189" s="15"/>
+      <x:c r="D189" s="15"/>
+      <x:c r="E189" s="15"/>
+      <x:c r="F189" s="17"/>
+      <x:c r="G189" s="15"/>
+    </x:row>
+    <x:row r="190">
+      <x:c r="A190" s="15"/>
+      <x:c r="B190" s="15"/>
+      <x:c r="C190" s="15"/>
+      <x:c r="D190" s="15"/>
+      <x:c r="E190" s="15"/>
+      <x:c r="F190" s="17"/>
+      <x:c r="G190" s="15"/>
+    </x:row>
+    <x:row r="191">
+      <x:c r="A191" s="15"/>
+      <x:c r="B191" s="15"/>
+      <x:c r="C191" s="15"/>
+      <x:c r="D191" s="15"/>
+      <x:c r="E191" s="15"/>
+      <x:c r="F191" s="17"/>
+      <x:c r="G191" s="15"/>
+    </x:row>
+    <x:row r="192">
+      <x:c r="A192" s="15"/>
+      <x:c r="B192" s="15"/>
+      <x:c r="C192" s="15"/>
+      <x:c r="D192" s="15"/>
+      <x:c r="E192" s="15"/>
+      <x:c r="F192" s="17"/>
+      <x:c r="G192" s="15"/>
+    </x:row>
+    <x:row r="193">
+      <x:c r="A193" s="15"/>
+      <x:c r="B193" s="15"/>
+      <x:c r="C193" s="15"/>
+      <x:c r="D193" s="15"/>
+      <x:c r="E193" s="15"/>
+      <x:c r="F193" s="17"/>
+      <x:c r="G193" s="15"/>
+    </x:row>
+    <x:row r="194">
+      <x:c r="A194" s="15"/>
+      <x:c r="B194" s="15"/>
+      <x:c r="C194" s="15"/>
+      <x:c r="D194" s="15"/>
+      <x:c r="E194" s="15"/>
+      <x:c r="F194" s="17"/>
+      <x:c r="G194" s="15"/>
+    </x:row>
+    <x:row r="195">
+      <x:c r="A195" s="15"/>
+      <x:c r="B195" s="15"/>
+      <x:c r="C195" s="15"/>
+      <x:c r="D195" s="15"/>
+      <x:c r="E195" s="15"/>
+      <x:c r="F195" s="17"/>
+      <x:c r="G195" s="15"/>
+    </x:row>
+    <x:row r="196">
+      <x:c r="A196" s="15"/>
+      <x:c r="B196" s="15"/>
+      <x:c r="C196" s="15"/>
+      <x:c r="D196" s="15"/>
+      <x:c r="E196" s="15"/>
+      <x:c r="F196" s="17"/>
+      <x:c r="G196" s="15"/>
+    </x:row>
+    <x:row r="197">
+      <x:c r="A197" s="15"/>
+      <x:c r="B197" s="15"/>
+      <x:c r="C197" s="15"/>
+      <x:c r="D197" s="15"/>
+      <x:c r="E197" s="15"/>
+      <x:c r="F197" s="17"/>
+      <x:c r="G197" s="15"/>
+    </x:row>
+    <x:row r="198">
+      <x:c r="A198" s="15"/>
+      <x:c r="B198" s="15"/>
+      <x:c r="C198" s="15"/>
+      <x:c r="D198" s="15"/>
+      <x:c r="E198" s="15"/>
+      <x:c r="F198" s="17"/>
+      <x:c r="G198" s="15"/>
+    </x:row>
+    <x:row r="199">
+      <x:c r="A199" s="15"/>
+      <x:c r="B199" s="15"/>
+      <x:c r="C199" s="15"/>
+      <x:c r="D199" s="15"/>
+      <x:c r="E199" s="15"/>
+      <x:c r="F199" s="17"/>
+      <x:c r="G199" s="15"/>
+    </x:row>
+    <x:row r="200">
+      <x:c r="A200" s="15"/>
+      <x:c r="B200" s="15"/>
+      <x:c r="C200" s="15"/>
+      <x:c r="D200" s="15"/>
+      <x:c r="E200" s="15"/>
+      <x:c r="F200" s="17"/>
+      <x:c r="G200" s="15"/>
+    </x:row>
+    <x:row r="201">
+      <x:c r="A201" s="15"/>
+      <x:c r="B201" s="15"/>
+      <x:c r="C201" s="15"/>
+      <x:c r="D201" s="15"/>
+      <x:c r="E201" s="15"/>
+      <x:c r="F201" s="17"/>
+      <x:c r="G201" s="15"/>
+    </x:row>
+    <x:row r="202">
+      <x:c r="A202" s="15"/>
+      <x:c r="B202" s="15"/>
+      <x:c r="C202" s="15"/>
+      <x:c r="D202" s="15"/>
+      <x:c r="E202" s="15"/>
+      <x:c r="F202" s="17"/>
+      <x:c r="G202" s="15"/>
+    </x:row>
+    <x:row r="203">
+      <x:c r="A203" s="15"/>
+      <x:c r="B203" s="15"/>
+      <x:c r="C203" s="15"/>
+      <x:c r="D203" s="15"/>
+      <x:c r="E203" s="15"/>
+      <x:c r="F203" s="17"/>
+      <x:c r="G203" s="15"/>
+    </x:row>
+    <x:row r="204">
+      <x:c r="A204" s="15"/>
+      <x:c r="B204" s="15"/>
+      <x:c r="C204" s="15"/>
+      <x:c r="D204" s="15"/>
+      <x:c r="E204" s="15"/>
+      <x:c r="F204" s="17"/>
+      <x:c r="G204" s="15"/>
+    </x:row>
+    <x:row r="205">
+      <x:c r="A205" s="15"/>
+      <x:c r="B205" s="15"/>
+      <x:c r="C205" s="15"/>
+      <x:c r="D205" s="15"/>
+      <x:c r="E205" s="15"/>
+      <x:c r="F205" s="17"/>
+      <x:c r="G205" s="15"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:H1"/>
-    <x:mergeCell ref="A3:H3"/>
+    <x:mergeCell ref="A1:G1"/>
+    <x:mergeCell ref="A3:G3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57f6028d33df4b9a"/>
+  </x:tableParts>
 </x:worksheet>
 </file>
 
@@ -584,52 +2373,119 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="82" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>So funktioniert der Import</x:v>
+        <x:v>Schäfchen · So funktioniert der Import</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
       <x:c r="D1" s="3"/>
       <x:c r="E1" s="3"/>
       <x:c r="F1" s="3"/>
-    </x:row>
-    <x:row r="3" ht="30" customHeight="1">
-      <x:c r="A3" s="15" t="str">
+      <x:c r="G1" s="3"/>
+    </x:row>
+    <x:row r="3" ht="25" customHeight="1">
+      <x:c r="A3" s="20" t="str">
         <x:v>1. Im Blatt „Baustellen“ jede Baustelle in eine eigene Zeile eintragen.</x:v>
       </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="15" t="str">
+      <x:c r="B3" s="20"/>
+      <x:c r="C3" s="20"/>
+      <x:c r="D3" s="20"/>
+      <x:c r="E3" s="20"/>
+      <x:c r="F3" s="20"/>
+      <x:c r="G3" s="20"/>
+    </x:row>
+    <x:row r="4" ht="25" customHeight="1">
+      <x:c r="A4" s="20" t="str">
         <x:v>2. Kunde, Baustelle, Straße, Hausnummer, PLZ und Ort sind Pflicht.</x:v>
       </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="15" t="str">
-        <x:v>3. Projekt und Aufgabe sind optional. Ohne Projekt wird der Baustellenname verwendet.</x:v>
+      <x:c r="B4" s="20"/>
+      <x:c r="C4" s="20"/>
+      <x:c r="D4" s="20"/>
+      <x:c r="E4" s="20"/>
+      <x:c r="F4" s="20"/>
+      <x:c r="G4" s="20"/>
+    </x:row>
+    <x:row r="5" ht="25" customHeight="1">
+      <x:c r="A5" s="20" t="str">
+        <x:v>3. Aufgabe ist optional und wird dem Monteur als Kurztext angezeigt.</x:v>
       </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="15" t="str">
+      <x:c r="B5" s="20"/>
+      <x:c r="C5" s="20"/>
+      <x:c r="D5" s="20"/>
+      <x:c r="E5" s="20"/>
+      <x:c r="F5" s="20"/>
+      <x:c r="G5" s="20"/>
+    </x:row>
+    <x:row r="6" ht="25" customHeight="1">
+      <x:c r="A6" s="20" t="str">
         <x:v>4. Die PLZ bleibt Text, damit führende Nullen erhalten bleiben.</x:v>
       </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="15" t="str">
+      <x:c r="B6" s="20"/>
+      <x:c r="C6" s="20"/>
+      <x:c r="D6" s="20"/>
+      <x:c r="E6" s="20"/>
+      <x:c r="F6" s="20"/>
+      <x:c r="G6" s="20"/>
+    </x:row>
+    <x:row r="7" ht="25" customHeight="1">
+      <x:c r="A7" s="20" t="str">
         <x:v>5. In Schäfchen zuerst die sichere Vorschau prüfen und danach bestätigen.</x:v>
       </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="15" t="str">
-        <x:v>6. Bereits vorhandene Baustellennamen werden nicht doppelt angelegt.</x:v>
+      <x:c r="B7" s="20"/>
+      <x:c r="C7" s="20"/>
+      <x:c r="D7" s="20"/>
+      <x:c r="E7" s="20"/>
+      <x:c r="F7" s="20"/>
+      <x:c r="G7" s="20"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="48" t="str">
+        <x:v>Einfach vor komplex: Kunde und Baustelle genügen. Schäfchen übernimmt die interne Zuordnung automatisch.</x:v>
       </x:c>
+      <x:c r="B10" s="49"/>
+      <x:c r="C10" s="49"/>
+      <x:c r="D10" s="49"/>
+      <x:c r="E10" s="49"/>
+      <x:c r="F10" s="49"/>
+      <x:c r="G10" s="50"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="51"/>
+      <x:c r="B11" s="52"/>
+      <x:c r="C11" s="52"/>
+      <x:c r="D11" s="52"/>
+      <x:c r="E11" s="52"/>
+      <x:c r="F11" s="52"/>
+      <x:c r="G11" s="53"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="54"/>
+      <x:c r="B12" s="55"/>
+      <x:c r="C12" s="55"/>
+      <x:c r="D12" s="55"/>
+      <x:c r="E12" s="55"/>
+      <x:c r="F12" s="55"/>
+      <x:c r="G12" s="56"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A1:G1"/>
+    <x:mergeCell ref="A3:G3"/>
+    <x:mergeCell ref="A4:G4"/>
+    <x:mergeCell ref="A5:G5"/>
+    <x:mergeCell ref="A6:G6"/>
+    <x:mergeCell ref="A7:G7"/>
+    <x:mergeCell ref="A10:G12"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
